--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/101.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/101.xlsx
@@ -426,13 +426,13 @@
         <v>-39.47398623332908</v>
       </c>
       <c r="E2">
-        <v>-18.17014855884607</v>
+        <v>-7.759119296022725</v>
       </c>
       <c r="F2">
-        <v>-2.44930611506885</v>
+        <v>1.419795901761358</v>
       </c>
       <c r="G2">
-        <v>-15.97309486897679</v>
+        <v>-17.35601672186786</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-38.32327654484878</v>
       </c>
       <c r="E3">
-        <v>-18.36326873223927</v>
+        <v>-7.67698123565159</v>
       </c>
       <c r="F3">
-        <v>-2.832264507220075</v>
+        <v>1.30124492927711</v>
       </c>
       <c r="G3">
-        <v>-16.33852340013951</v>
+        <v>-16.77150886371417</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-36.85039937289229</v>
       </c>
       <c r="E4">
-        <v>-19.20980118373378</v>
+        <v>-8.857153612503543</v>
       </c>
       <c r="F4">
-        <v>-2.130105505176296</v>
+        <v>0.8960307901148699</v>
       </c>
       <c r="G4">
-        <v>-15.71777579631657</v>
+        <v>-16.22304625075768</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-35.28069383103004</v>
       </c>
       <c r="E5">
-        <v>-20.38376866286644</v>
+        <v>-9.754820401829335</v>
       </c>
       <c r="F5">
-        <v>-1.838908683702783</v>
+        <v>1.849186771941704</v>
       </c>
       <c r="G5">
-        <v>-14.19337116717159</v>
+        <v>-15.72631032038492</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-33.64758871572825</v>
       </c>
       <c r="E6">
-        <v>-19.46170175700728</v>
+        <v>-10.79228843756018</v>
       </c>
       <c r="F6">
-        <v>-2.354443136835056</v>
+        <v>1.960181376977616</v>
       </c>
       <c r="G6">
-        <v>-13.95870047348249</v>
+        <v>-15.40703975359309</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-32.06578929968908</v>
       </c>
       <c r="E7">
-        <v>-21.84466905279753</v>
+        <v>-12.21029861413976</v>
       </c>
       <c r="F7">
-        <v>-2.215569826857927</v>
+        <v>1.376374539241414</v>
       </c>
       <c r="G7">
-        <v>-13.70500658933024</v>
+        <v>-14.24882729840373</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-30.59486428750307</v>
       </c>
       <c r="E8">
-        <v>-21.02961794314523</v>
+        <v>-12.26781228456599</v>
       </c>
       <c r="F8">
-        <v>-2.377103955506039</v>
+        <v>1.752676999311145</v>
       </c>
       <c r="G8">
-        <v>-13.22610987674856</v>
+        <v>-13.36072117323865</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-29.26819251051804</v>
       </c>
       <c r="E9">
-        <v>-20.4967567769584</v>
+        <v>-13.09268158579019</v>
       </c>
       <c r="F9">
-        <v>-2.639510867895255</v>
+        <v>1.671134168914367</v>
       </c>
       <c r="G9">
-        <v>-14.18368008324938</v>
+        <v>-12.16892540500151</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-28.12747850689145</v>
       </c>
       <c r="E10">
-        <v>-20.78688350726562</v>
+        <v>-14.20448795102414</v>
       </c>
       <c r="F10">
-        <v>-2.121981706057042</v>
+        <v>1.631536550325745</v>
       </c>
       <c r="G10">
-        <v>-12.51625103316944</v>
+        <v>-11.87647893351107</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-27.14883010175547</v>
       </c>
       <c r="E11">
-        <v>-22.41178590599154</v>
+        <v>-14.75488812863572</v>
       </c>
       <c r="F11">
-        <v>-2.626838503367229</v>
+        <v>1.592644700764309</v>
       </c>
       <c r="G11">
-        <v>-12.5213759248018</v>
+        <v>-11.33950359675548</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-26.35582352798065</v>
       </c>
       <c r="E12">
-        <v>-24.30477809573514</v>
+        <v>-15.25911705594917</v>
       </c>
       <c r="F12">
-        <v>-1.481886474933211</v>
+        <v>1.974387877935627</v>
       </c>
       <c r="G12">
-        <v>-11.37958766383513</v>
+        <v>-10.53003179330244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-25.69971163157465</v>
       </c>
       <c r="E13">
-        <v>-24.53803490337149</v>
+        <v>-15.99568493119619</v>
       </c>
       <c r="F13">
-        <v>-1.927254067211351</v>
+        <v>1.916007856855929</v>
       </c>
       <c r="G13">
-        <v>-11.07169863808826</v>
+        <v>-9.666717298774573</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-25.17449729769753</v>
       </c>
       <c r="E14">
-        <v>-24.43022169059026</v>
+        <v>-17.54136897711233</v>
       </c>
       <c r="F14">
-        <v>-1.486690177502045</v>
+        <v>2.24612055054556</v>
       </c>
       <c r="G14">
-        <v>-8.737686446771502</v>
+        <v>-8.70171691316744</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-24.72645750378182</v>
       </c>
       <c r="E15">
-        <v>-24.72870052887171</v>
+        <v>-19.1554398007031</v>
       </c>
       <c r="F15">
-        <v>-1.733153502489579</v>
+        <v>2.490053213117542</v>
       </c>
       <c r="G15">
-        <v>-9.060565062588255</v>
+        <v>-8.245471020658254</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-24.29951994486025</v>
       </c>
       <c r="E16">
-        <v>-28.01202174171492</v>
+        <v>-19.14102400419462</v>
       </c>
       <c r="F16">
-        <v>-1.205326905467165</v>
+        <v>2.427602594620487</v>
       </c>
       <c r="G16">
-        <v>-8.728822968884673</v>
+        <v>-7.033505945082463</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-23.859463126185</v>
       </c>
       <c r="E17">
-        <v>-28.29624675872956</v>
+        <v>-20.71792358642817</v>
       </c>
       <c r="F17">
-        <v>-1.271178800520114</v>
+        <v>2.868837461926061</v>
       </c>
       <c r="G17">
-        <v>-9.41063849943834</v>
+        <v>-6.889700911514761</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-23.34552750162183</v>
       </c>
       <c r="E18">
-        <v>-28.91872176567221</v>
+        <v>-20.66753267342402</v>
       </c>
       <c r="F18">
-        <v>-1.002655223228627</v>
+        <v>2.694293823216982</v>
       </c>
       <c r="G18">
-        <v>-8.576600894755222</v>
+        <v>-6.695312701494239</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-22.75123821665774</v>
       </c>
       <c r="E19">
-        <v>-29.60451247926187</v>
+        <v>-21.86752002150673</v>
       </c>
       <c r="F19">
-        <v>-0.8085670840178968</v>
+        <v>3.046210803683102</v>
       </c>
       <c r="G19">
-        <v>-7.839975392255721</v>
+        <v>-6.102036657631292</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-22.03744273097638</v>
       </c>
       <c r="E20">
-        <v>-28.48619387867059</v>
+        <v>-22.70020151323293</v>
       </c>
       <c r="F20">
-        <v>-1.27538525019153</v>
+        <v>3.056842070930631</v>
       </c>
       <c r="G20">
-        <v>-7.120582109429864</v>
+        <v>-5.618939257002507</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-21.22626206713085</v>
       </c>
       <c r="E21">
-        <v>-29.97254930081155</v>
+        <v>-22.98268218149115</v>
       </c>
       <c r="F21">
-        <v>-1.604826966284894</v>
+        <v>2.987906992404461</v>
       </c>
       <c r="G21">
-        <v>-8.730372445799498</v>
+        <v>-4.808318725929378</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.32384663587822</v>
       </c>
       <c r="E22">
-        <v>-30.97682279502871</v>
+        <v>-23.48807816118688</v>
       </c>
       <c r="F22">
-        <v>-1.308130613624195</v>
+        <v>3.018664274070407</v>
       </c>
       <c r="G22">
-        <v>-6.740770986314703</v>
+        <v>-4.538177150853113</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.36694149361961</v>
       </c>
       <c r="E23">
-        <v>-30.38125229104829</v>
+        <v>-24.45906159002987</v>
       </c>
       <c r="F23">
-        <v>-0.5716192153863205</v>
+        <v>3.333165555686878</v>
       </c>
       <c r="G23">
-        <v>-8.016164101731592</v>
+        <v>-4.95840782172789</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.40507961567324</v>
       </c>
       <c r="E24">
-        <v>-30.74783133542296</v>
+        <v>-23.58266339589852</v>
       </c>
       <c r="F24">
-        <v>-0.9180018732343367</v>
+        <v>3.066573731178719</v>
       </c>
       <c r="G24">
-        <v>-8.179041929909673</v>
+        <v>-4.535830091465702</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.47256157163383</v>
       </c>
       <c r="E25">
-        <v>-32.44028986955854</v>
+        <v>-24.71314259924891</v>
       </c>
       <c r="F25">
-        <v>-1.708637969203728</v>
+        <v>3.08697310684006</v>
       </c>
       <c r="G25">
-        <v>-7.265541092106838</v>
+        <v>-4.086899505300817</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.63667983920688</v>
       </c>
       <c r="E26">
-        <v>-30.0664824813452</v>
+        <v>-23.93120919670079</v>
       </c>
       <c r="F26">
-        <v>-1.216691277866171</v>
+        <v>3.134451812898917</v>
       </c>
       <c r="G26">
-        <v>-7.671440080548699</v>
+        <v>-5.046382082214635</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.92038567108106</v>
       </c>
       <c r="E27">
-        <v>-31.76536603340029</v>
+        <v>-24.13040551826222</v>
       </c>
       <c r="F27">
-        <v>-1.117669066902921</v>
+        <v>2.842311480953615</v>
       </c>
       <c r="G27">
-        <v>-6.582614689729652</v>
+        <v>-5.160805796153947</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.37824635034815</v>
       </c>
       <c r="E28">
-        <v>-30.62450795494917</v>
+        <v>-24.18045586793772</v>
       </c>
       <c r="F28">
-        <v>-1.459208260546768</v>
+        <v>2.780861530279142</v>
       </c>
       <c r="G28">
-        <v>-7.320724400529199</v>
+        <v>-5.046588331037333</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.01736498739155</v>
       </c>
       <c r="E29">
-        <v>-29.26003267234662</v>
+        <v>-23.37745322433875</v>
       </c>
       <c r="F29">
-        <v>-0.89707399917001</v>
+        <v>2.7303394023824</v>
       </c>
       <c r="G29">
-        <v>-8.456767718023121</v>
+        <v>-4.737880836861142</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.85755705197436</v>
       </c>
       <c r="E30">
-        <v>-30.13483603332923</v>
+        <v>-22.71753286409144</v>
       </c>
       <c r="F30">
-        <v>-1.066082486893582</v>
+        <v>2.526663738851669</v>
       </c>
       <c r="G30">
-        <v>-7.646173294395904</v>
+        <v>-4.38201024164649</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.89820196583066</v>
       </c>
       <c r="E31">
-        <v>-29.69887967037896</v>
+        <v>-23.2992108761903</v>
       </c>
       <c r="F31">
-        <v>-1.225746161946173</v>
+        <v>2.296367660464572</v>
       </c>
       <c r="G31">
-        <v>-8.691253048846256</v>
+        <v>-5.035761573217985</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.11160875146261</v>
       </c>
       <c r="E32">
-        <v>-29.87183600279013</v>
+        <v>-22.94245417659886</v>
       </c>
       <c r="F32">
-        <v>-0.8310638859431257</v>
+        <v>2.124168301505417</v>
       </c>
       <c r="G32">
-        <v>-8.46478531466243</v>
+        <v>-5.41375300735314</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.49282607372066</v>
       </c>
       <c r="E33">
-        <v>-28.59987973226512</v>
+        <v>-21.98306236056346</v>
       </c>
       <c r="F33">
-        <v>-1.461480472332648</v>
+        <v>2.36446774464872</v>
       </c>
       <c r="G33">
-        <v>-9.264225332024116</v>
+        <v>-5.436518700187648</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.99200360100191</v>
       </c>
       <c r="E34">
-        <v>-28.19368320506292</v>
+        <v>-20.69383080753284</v>
       </c>
       <c r="F34">
-        <v>-1.717200803046466</v>
+        <v>2.739829179348871</v>
       </c>
       <c r="G34">
-        <v>-8.5434392169589</v>
+        <v>-4.875310432137345</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.59613559061252</v>
       </c>
       <c r="E35">
-        <v>-30.1739987395167</v>
+        <v>-21.15523597287599</v>
       </c>
       <c r="F35">
-        <v>-1.064692486391684</v>
+        <v>2.297815646684666</v>
       </c>
       <c r="G35">
-        <v>-7.94709685357369</v>
+        <v>-5.286434825878318</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.25437602402028</v>
       </c>
       <c r="E36">
-        <v>-28.15954588457849</v>
+        <v>-19.13160452090991</v>
       </c>
       <c r="F36">
-        <v>-1.017715770978924</v>
+        <v>2.570206043012422</v>
       </c>
       <c r="G36">
-        <v>-8.739119745552024</v>
+        <v>-5.908807618209224</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.94640083295601</v>
       </c>
       <c r="E37">
-        <v>-27.07803927256483</v>
+        <v>-19.30103893011761</v>
       </c>
       <c r="F37">
-        <v>-0.8482806740429106</v>
+        <v>2.986859936007323</v>
       </c>
       <c r="G37">
-        <v>-9.250176915379337</v>
+        <v>-6.354072718968186</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-18.64095046344293</v>
       </c>
       <c r="E38">
-        <v>-26.71993693250413</v>
+        <v>-18.53303124514164</v>
       </c>
       <c r="F38">
-        <v>-1.181410281813537</v>
+        <v>2.96978562710082</v>
       </c>
       <c r="G38">
-        <v>-8.418551638698405</v>
+        <v>-6.349832869752218</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-19.30528449017807</v>
       </c>
       <c r="E39">
-        <v>-26.77970164346842</v>
+        <v>-18.16896904682982</v>
       </c>
       <c r="F39">
-        <v>-0.8631349583099114</v>
+        <v>2.855517314089044</v>
       </c>
       <c r="G39">
-        <v>-8.722196899112427</v>
+        <v>-6.56235009021343</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-19.93489413963695</v>
       </c>
       <c r="E40">
-        <v>-24.6429533278593</v>
+        <v>-16.59273397840824</v>
       </c>
       <c r="F40">
-        <v>-0.888381111645032</v>
+        <v>2.783321781465456</v>
       </c>
       <c r="G40">
-        <v>-10.55396840508606</v>
+        <v>-6.46774975995444</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-20.49852223885084</v>
       </c>
       <c r="E41">
-        <v>-24.80133604173164</v>
+        <v>-16.43427235352074</v>
       </c>
       <c r="F41">
-        <v>-0.6580982871363806</v>
+        <v>2.879170516908582</v>
       </c>
       <c r="G41">
-        <v>-9.53853626621239</v>
+        <v>-6.997018178677063</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-21.00927781858768</v>
       </c>
       <c r="E42">
-        <v>-24.02398778448613</v>
+        <v>-16.17594676232773</v>
       </c>
       <c r="F42">
-        <v>-0.9754905709886224</v>
+        <v>2.966672622401099</v>
       </c>
       <c r="G42">
-        <v>-10.73354716641349</v>
+        <v>-7.114867189519917</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-21.44811953119522</v>
       </c>
       <c r="E43">
-        <v>-24.14881670406518</v>
+        <v>-15.09410166359109</v>
       </c>
       <c r="F43">
-        <v>-0.7414535854104837</v>
+        <v>2.966694159953572</v>
       </c>
       <c r="G43">
-        <v>-10.21360171662573</v>
+        <v>-7.344040960472433</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-21.83305148579916</v>
       </c>
       <c r="E44">
-        <v>-23.3083271750483</v>
+        <v>-15.72876219256079</v>
       </c>
       <c r="F44">
-        <v>-0.6125223410017546</v>
+        <v>2.980575940889686</v>
       </c>
       <c r="G44">
-        <v>-9.843113562445438</v>
+        <v>-7.82525731962332</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-22.16298442831716</v>
       </c>
       <c r="E45">
-        <v>-21.37325464816154</v>
+        <v>-13.40168050835743</v>
       </c>
       <c r="F45">
-        <v>-0.4508498749973751</v>
+        <v>3.027125218722601</v>
       </c>
       <c r="G45">
-        <v>-9.864248845282797</v>
+        <v>-7.882769412220955</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-22.44669734868845</v>
       </c>
       <c r="E46">
-        <v>-22.48735773925812</v>
+        <v>-13.39615673729541</v>
       </c>
       <c r="F46">
-        <v>-0.8177222005536369</v>
+        <v>3.138469394802494</v>
       </c>
       <c r="G46">
-        <v>-10.41899029898091</v>
+        <v>-8.202209677411211</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-22.70502481203524</v>
       </c>
       <c r="E47">
-        <v>-20.78693334580152</v>
+        <v>-13.00371564600104</v>
       </c>
       <c r="F47">
-        <v>-0.8385713797146976</v>
+        <v>3.432172027669476</v>
       </c>
       <c r="G47">
-        <v>-9.902645065984299</v>
+        <v>-8.668681856483786</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-22.93215907406381</v>
       </c>
       <c r="E48">
-        <v>-21.39046555589163</v>
+        <v>-12.85929602860277</v>
       </c>
       <c r="F48">
-        <v>-1.057575982034234</v>
+        <v>3.288461880427401</v>
       </c>
       <c r="G48">
-        <v>-11.95364862750749</v>
+        <v>-8.929685825491156</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-23.16246885815641</v>
       </c>
       <c r="E49">
-        <v>-21.93564099365657</v>
+        <v>-12.07154813019989</v>
       </c>
       <c r="F49">
-        <v>0.09418771155300444</v>
+        <v>3.414191484824309</v>
       </c>
       <c r="G49">
-        <v>-11.15135245556312</v>
+        <v>-9.124589657568423</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-23.38405797569436</v>
       </c>
       <c r="E50">
-        <v>-21.17249671914198</v>
+        <v>-11.00966751830171</v>
       </c>
       <c r="F50">
-        <v>-0.1302948844012448</v>
+        <v>3.33170431558834</v>
       </c>
       <c r="G50">
-        <v>-11.05070564083112</v>
+        <v>-9.271043291523808</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-23.62451684661331</v>
       </c>
       <c r="E51">
-        <v>-19.90945116351439</v>
+        <v>-10.85322020090674</v>
       </c>
       <c r="F51">
-        <v>0.02037934759616569</v>
+        <v>2.985231365693419</v>
       </c>
       <c r="G51">
-        <v>-10.32674486034311</v>
+        <v>-9.182544271374251</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-23.86832976250623</v>
       </c>
       <c r="E52">
-        <v>-19.71329914585407</v>
+        <v>-10.31440332968011</v>
       </c>
       <c r="F52">
-        <v>-0.6908983228176299</v>
+        <v>3.146630470454875</v>
       </c>
       <c r="G52">
-        <v>-10.464645695018</v>
+        <v>-9.578035526503637</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-24.12359564680846</v>
       </c>
       <c r="E53">
-        <v>-18.00024483675866</v>
+        <v>-9.163560931204094</v>
       </c>
       <c r="F53">
-        <v>-0.435315501092676</v>
+        <v>3.231640846799771</v>
       </c>
       <c r="G53">
-        <v>-12.69844706594947</v>
+        <v>-9.995795127622925</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-24.38487354143297</v>
       </c>
       <c r="E54">
-        <v>-17.88381371047842</v>
+        <v>-8.729027043132584</v>
       </c>
       <c r="F54">
-        <v>-0.2726523076745482</v>
+        <v>3.166900620801379</v>
       </c>
       <c r="G54">
-        <v>-13.02792433872026</v>
+        <v>-9.975178077586904</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-24.62852026250961</v>
       </c>
       <c r="E55">
-        <v>-19.48008802354229</v>
+        <v>-8.692250356851227</v>
       </c>
       <c r="F55">
-        <v>-0.5024016635757967</v>
+        <v>2.907366486565071</v>
       </c>
       <c r="G55">
-        <v>-12.36128245573014</v>
+        <v>-10.58573725064302</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-24.86266084840513</v>
       </c>
       <c r="E56">
-        <v>-19.51179779200736</v>
+        <v>-7.303021934752704</v>
       </c>
       <c r="F56">
-        <v>-0.5077438049564508</v>
+        <v>3.095571560481119</v>
       </c>
       <c r="G56">
-        <v>-11.70681447476839</v>
+        <v>-10.50921893742208</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-25.0514360610678</v>
       </c>
       <c r="E57">
-        <v>-17.88025856158437</v>
+        <v>-7.860632087224183</v>
       </c>
       <c r="F57">
-        <v>-0.5689866637802238</v>
+        <v>3.096905231999626</v>
       </c>
       <c r="G57">
-        <v>-11.91004527671901</v>
+        <v>-10.84953210561829</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-25.20577453751957</v>
       </c>
       <c r="E58">
-        <v>-18.12190900930819</v>
+        <v>-7.638235927202265</v>
       </c>
       <c r="F58">
-        <v>-0.4080953482366842</v>
+        <v>3.03829492478195</v>
       </c>
       <c r="G58">
-        <v>-11.98611454187028</v>
+        <v>-10.61346074745605</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-25.29357530314875</v>
       </c>
       <c r="E59">
-        <v>-16.74351631555614</v>
+        <v>-6.401027499226441</v>
       </c>
       <c r="F59">
-        <v>-0.2422371417459588</v>
+        <v>3.100878082063452</v>
       </c>
       <c r="G59">
-        <v>-13.19668809057901</v>
+        <v>-10.960371267234</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-25.32450769907718</v>
       </c>
       <c r="E60">
-        <v>-17.77905310802094</v>
+        <v>-6.009387977717759</v>
       </c>
       <c r="F60">
-        <v>-0.06168535426437573</v>
+        <v>3.205716260561758</v>
       </c>
       <c r="G60">
-        <v>-12.86713119009818</v>
+        <v>-10.79953373595388</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-25.28546173785192</v>
       </c>
       <c r="E61">
-        <v>-16.44237526881547</v>
+        <v>-5.255322623159239</v>
       </c>
       <c r="F61">
-        <v>-0.6042842271809135</v>
+        <v>2.753899828052823</v>
       </c>
       <c r="G61">
-        <v>-12.2126710413702</v>
+        <v>-11.18268922289026</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-25.17214690510261</v>
       </c>
       <c r="E62">
-        <v>-17.51339294562829</v>
+        <v>-6.375593233073191</v>
       </c>
       <c r="F62">
-        <v>-0.4901343707077389</v>
+        <v>2.873748023889856</v>
       </c>
       <c r="G62">
-        <v>-12.52026505297828</v>
+        <v>-11.05719334114003</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-24.99801760805826</v>
       </c>
       <c r="E63">
-        <v>-16.76862663122606</v>
+        <v>-5.367289047265293</v>
       </c>
       <c r="F63">
-        <v>-0.6446878472524594</v>
+        <v>2.784905619939609</v>
       </c>
       <c r="G63">
-        <v>-12.65196406387699</v>
+        <v>-11.07254713008037</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-24.74955394619227</v>
       </c>
       <c r="E64">
-        <v>-14.15952528522154</v>
+        <v>-6.013910824850497</v>
       </c>
       <c r="F64">
-        <v>-0.6494766392080433</v>
+        <v>2.67541201663757</v>
       </c>
       <c r="G64">
-        <v>-12.51975856852761</v>
+        <v>-11.26532451068817</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-24.45683312078819</v>
       </c>
       <c r="E65">
-        <v>-15.33930310699764</v>
+        <v>-5.374935109314301</v>
       </c>
       <c r="F65">
-        <v>-0.07272169317187355</v>
+        <v>3.030683885085028</v>
       </c>
       <c r="G65">
-        <v>-11.91878082812087</v>
+        <v>-10.82436713850455</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-24.10722930021324</v>
       </c>
       <c r="E66">
-        <v>-15.95212605082139</v>
+        <v>-5.038047372700834</v>
       </c>
       <c r="F66">
-        <v>-0.969707738149679</v>
+        <v>2.775089466216435</v>
       </c>
       <c r="G66">
-        <v>-12.55585211249975</v>
+        <v>-10.87693709159121</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-23.7340066687645</v>
       </c>
       <c r="E67">
-        <v>-16.97035641169563</v>
+        <v>-6.368433096749187</v>
       </c>
       <c r="F67">
-        <v>-0.8535167843960063</v>
+        <v>2.432163585540301</v>
       </c>
       <c r="G67">
-        <v>-13.52264999575786</v>
+        <v>-10.69741707201707</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-23.33487456609188</v>
       </c>
       <c r="E68">
-        <v>-14.86677148851527</v>
+        <v>-5.264704727542028</v>
       </c>
       <c r="F68">
-        <v>-1.312148195527772</v>
+        <v>2.693786862366469</v>
       </c>
       <c r="G68">
-        <v>-12.92837403671652</v>
+        <v>-11.08244707356987</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-22.93319375077433</v>
       </c>
       <c r="E69">
-        <v>-13.94271934764284</v>
+        <v>-6.010567489734011</v>
       </c>
       <c r="F69">
-        <v>-0.6935143070756706</v>
+        <v>2.614657894581449</v>
       </c>
       <c r="G69">
-        <v>-11.91454881113868</v>
+        <v>-10.79937317516153</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.54449143290883</v>
       </c>
       <c r="E70">
-        <v>-15.68082167423829</v>
+        <v>-5.383980803579778</v>
       </c>
       <c r="F70">
-        <v>-1.213145037014786</v>
+        <v>2.235442894723474</v>
       </c>
       <c r="G70">
-        <v>-11.62666461582121</v>
+        <v>-10.55103392816565</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.16211559138536</v>
       </c>
       <c r="E71">
-        <v>-15.41241623915992</v>
+        <v>-6.622443501375701</v>
       </c>
       <c r="F71">
-        <v>-0.505226396419343</v>
+        <v>2.512594746882522</v>
       </c>
       <c r="G71">
-        <v>-12.26729434507777</v>
+        <v>-10.2070004489271</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.80639201045713</v>
       </c>
       <c r="E72">
-        <v>-14.83692235872373</v>
+        <v>-6.517608141114378</v>
       </c>
       <c r="F72">
-        <v>-0.8792922645015158</v>
+        <v>2.462675670455018</v>
       </c>
       <c r="G72">
-        <v>-12.45571961445219</v>
+        <v>-9.980030146409488</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.4539485403883</v>
       </c>
       <c r="E73">
-        <v>-16.67023290172954</v>
+        <v>-6.777005260829195</v>
       </c>
       <c r="F73">
-        <v>-1.212282706548472</v>
+        <v>2.219496822219584</v>
       </c>
       <c r="G73">
-        <v>-12.77217318783021</v>
+        <v>-9.770686285998774</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.12408133588655</v>
       </c>
       <c r="E74">
-        <v>-15.79968658235488</v>
+        <v>-6.820975309125155</v>
       </c>
       <c r="F74">
-        <v>-0.6609387589605801</v>
+        <v>2.249018179720553</v>
       </c>
       <c r="G74">
-        <v>-11.08166515556483</v>
+        <v>-9.183767405215187</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-20.79247708843722</v>
       </c>
       <c r="E75">
-        <v>-16.43336695345192</v>
+        <v>-7.433524141001466</v>
       </c>
       <c r="F75">
-        <v>-0.7954034976200098</v>
+        <v>2.225108183006148</v>
       </c>
       <c r="G75">
-        <v>-11.52787142974889</v>
+        <v>-9.54470806642578</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-20.47327982484577</v>
       </c>
       <c r="E76">
-        <v>-15.70837823137853</v>
+        <v>-7.233904191884907</v>
       </c>
       <c r="F76">
-        <v>-1.378968452074594</v>
+        <v>2.139995089103304</v>
       </c>
       <c r="G76">
-        <v>-11.59986532259343</v>
+        <v>-8.382524668713337</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.1601918857939</v>
       </c>
       <c r="E77">
-        <v>-16.10115157957889</v>
+        <v>-7.777655078165434</v>
       </c>
       <c r="F77">
-        <v>-1.112705489425347</v>
+        <v>2.090886155995738</v>
       </c>
       <c r="G77">
-        <v>-10.86735304819723</v>
+        <v>-8.323610606270275</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-19.84782739794405</v>
       </c>
       <c r="E78">
-        <v>-17.96623418921964</v>
+        <v>-8.188013123115118</v>
       </c>
       <c r="F78">
-        <v>-0.8674648347243444</v>
+        <v>1.993675584542411</v>
       </c>
       <c r="G78">
-        <v>-12.5036032809978</v>
+        <v>-7.412554730777019</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-19.547948343055</v>
       </c>
       <c r="E79">
-        <v>-18.81492631060306</v>
+        <v>-7.927311895044306</v>
       </c>
       <c r="F79">
-        <v>-1.0339534288086</v>
+        <v>1.921024449847283</v>
       </c>
       <c r="G79">
-        <v>-10.60079472007227</v>
+        <v>-7.501622893247439</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-19.24215461518538</v>
       </c>
       <c r="E80">
-        <v>-18.54446088270757</v>
+        <v>-8.968243709020058</v>
       </c>
       <c r="F80">
-        <v>-1.233505479408196</v>
+        <v>2.038014778144657</v>
       </c>
       <c r="G80">
-        <v>-11.55590560516826</v>
+        <v>-7.751074317439132</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-18.9494761281572</v>
       </c>
       <c r="E81">
-        <v>-17.53565000511804</v>
+        <v>-10.41257278576508</v>
       </c>
       <c r="F81">
-        <v>-0.9286165731338095</v>
+        <v>2.167911070577647</v>
       </c>
       <c r="G81">
-        <v>-9.997134439598167</v>
+        <v>-6.723829864662969</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-18.65071127444435</v>
       </c>
       <c r="E82">
-        <v>-16.61176399269861</v>
+        <v>-10.87256170604647</v>
       </c>
       <c r="F82">
-        <v>-1.897282077843259</v>
+        <v>2.054457871090227</v>
       </c>
       <c r="G82">
-        <v>-10.4729034801597</v>
+        <v>-6.597088657742784</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-18.36407673405504</v>
       </c>
       <c r="E83">
-        <v>-17.74394185948084</v>
+        <v>-12.16691001542928</v>
       </c>
       <c r="F83">
-        <v>-1.515630021086248</v>
+        <v>1.77200943775768</v>
       </c>
       <c r="G83">
-        <v>-10.98101964620512</v>
+        <v>-6.950056104972117</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.08130906224564</v>
       </c>
       <c r="E84">
-        <v>-21.04099358896393</v>
+        <v>-12.9271304291712</v>
       </c>
       <c r="F84">
-        <v>-0.7470550057882139</v>
+        <v>1.998311128528477</v>
       </c>
       <c r="G84">
-        <v>-10.10086454369228</v>
+        <v>-5.539248889103365</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.80840873218789</v>
       </c>
       <c r="E85">
-        <v>-22.44253212942925</v>
+        <v>-14.02484079516868</v>
       </c>
       <c r="F85">
-        <v>-0.9007751447257182</v>
+        <v>1.946821467505265</v>
       </c>
       <c r="G85">
-        <v>-9.829635593493816</v>
+        <v>-5.949707542973605</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.55551686430617</v>
       </c>
       <c r="E86">
-        <v>-22.5399124753625</v>
+        <v>-14.33370681497353</v>
       </c>
       <c r="F86">
-        <v>-1.205761798353635</v>
+        <v>1.696015012224853</v>
       </c>
       <c r="G86">
-        <v>-9.272047122819092</v>
+        <v>-5.993959663792975</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.31332771318591</v>
       </c>
       <c r="E87">
-        <v>-22.24137133891118</v>
+        <v>-15.73988449248868</v>
       </c>
       <c r="F87">
-        <v>-2.395612168386788</v>
+        <v>1.720904139209367</v>
       </c>
       <c r="G87">
-        <v>-9.000649779594502</v>
+        <v>-6.200352077443435</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.10246680509765</v>
       </c>
       <c r="E88">
-        <v>-25.52632891701636</v>
+        <v>-17.03648799562087</v>
       </c>
       <c r="F88">
-        <v>-1.419027471306576</v>
+        <v>1.673995349923637</v>
       </c>
       <c r="G88">
-        <v>-8.62104751604663</v>
+        <v>-5.098116597032135</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.90858960166118</v>
       </c>
       <c r="E89">
-        <v>-25.48126242093064</v>
+        <v>-18.33293782993405</v>
       </c>
       <c r="F89">
-        <v>-0.7593670304960229</v>
+        <v>1.894972295029238</v>
       </c>
       <c r="G89">
-        <v>-9.394310902765518</v>
+        <v>-5.240971319568672</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.75299464980572</v>
       </c>
       <c r="E90">
-        <v>-25.03910739007808</v>
+        <v>-20.12691330848241</v>
       </c>
       <c r="F90">
-        <v>-1.504165416231503</v>
+        <v>1.684760812690419</v>
       </c>
       <c r="G90">
-        <v>-8.756144411030673</v>
+        <v>-4.509445906627912</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.62398389809933</v>
       </c>
       <c r="E91">
-        <v>-28.61817670475666</v>
+        <v>-21.89765572287969</v>
       </c>
       <c r="F91">
-        <v>-1.71400910344348</v>
+        <v>1.419030490281171</v>
       </c>
       <c r="G91">
-        <v>-8.506183891643714</v>
+        <v>-4.684611204224066</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.53179738108314</v>
       </c>
       <c r="E92">
-        <v>-29.1875404452774</v>
+        <v>-24.1440695835209</v>
       </c>
       <c r="F92">
-        <v>-2.504435622459962</v>
+        <v>1.847024733020397</v>
       </c>
       <c r="G92">
-        <v>-9.464019088720539</v>
+        <v>-4.252838431511978</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.47494479172646</v>
       </c>
       <c r="E93">
-        <v>-30.11689416040597</v>
+        <v>-24.77450629657325</v>
       </c>
       <c r="F93">
-        <v>-1.229932730799921</v>
+        <v>1.421573578207766</v>
       </c>
       <c r="G93">
-        <v>-8.829015514057827</v>
+        <v>-4.488583446600325</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.43909109177427</v>
       </c>
       <c r="E94">
-        <v>-32.95039351429097</v>
+        <v>-27.7733823722016</v>
       </c>
       <c r="F94">
-        <v>-1.337646172553344</v>
+        <v>1.699722784719784</v>
       </c>
       <c r="G94">
-        <v>-8.064730477987776</v>
+        <v>-4.713282401323672</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-16.43015179176174</v>
       </c>
       <c r="E95">
-        <v>-32.55700964402586</v>
+        <v>-29.242917288477</v>
       </c>
       <c r="F95">
-        <v>-1.718771387642174</v>
+        <v>1.395975368726456</v>
       </c>
       <c r="G95">
-        <v>-9.495738330130269</v>
+        <v>-4.672382476559291</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-16.42085255045921</v>
       </c>
       <c r="E96">
-        <v>-37.03052493264783</v>
+        <v>-31.13140739714449</v>
       </c>
       <c r="F96">
-        <v>-2.469444554998308</v>
+        <v>1.488469216188243</v>
       </c>
       <c r="G96">
-        <v>-9.055895745887049</v>
+        <v>-5.005602251701445</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.41408363585661</v>
       </c>
       <c r="E97">
-        <v>-38.54373086600381</v>
+        <v>-34.05619848916054</v>
       </c>
       <c r="F97">
-        <v>-1.588451799466353</v>
+        <v>1.323292756070021</v>
       </c>
       <c r="G97">
-        <v>-9.618361087457973</v>
+        <v>-5.023846134904145</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.38008469912038</v>
       </c>
       <c r="E98">
-        <v>-40.30794443219845</v>
+        <v>-36.48293647910316</v>
       </c>
       <c r="F98">
-        <v>-2.811878385437179</v>
+        <v>1.239248256116789</v>
       </c>
       <c r="G98">
-        <v>-9.790320390696241</v>
+        <v>-5.394146315473879</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.31776177373562</v>
       </c>
       <c r="E99">
-        <v>-41.42514997215468</v>
+        <v>-38.09449045663108</v>
       </c>
       <c r="F99">
-        <v>-2.589386356351857</v>
+        <v>0.8904757583116963</v>
       </c>
       <c r="G99">
-        <v>-9.518832976783257</v>
+        <v>-5.241892912409335</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.21312747320531</v>
       </c>
       <c r="E100">
-        <v>-43.02656180762737</v>
+        <v>-41.20640863809861</v>
       </c>
       <c r="F100">
-        <v>-1.958972255064544</v>
+        <v>0.6719358701051308</v>
       </c>
       <c r="G100">
-        <v>-9.233834959611261</v>
+        <v>-5.536886165248407</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.05949602713645</v>
       </c>
       <c r="E101">
-        <v>-44.07486972491601</v>
+        <v>-42.73971819087242</v>
       </c>
       <c r="F101">
-        <v>-2.952415885526532</v>
+        <v>0.6927585415093021</v>
       </c>
       <c r="G101">
-        <v>-10.61433143077719</v>
+        <v>-5.392887936580963</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.87051182508299</v>
       </c>
       <c r="E102">
-        <v>-48.33142748374593</v>
+        <v>-44.5117086452728</v>
       </c>
       <c r="F102">
-        <v>-3.317720939956697</v>
+        <v>0.2797196438602181</v>
       </c>
       <c r="G102">
-        <v>-11.0491522477994</v>
+        <v>-5.99709255730231</v>
       </c>
     </row>
   </sheetData>
